--- a/leads_output.xlsx
+++ b/leads_output.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -633,7 +633,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I3" s="3" t="b">
@@ -678,7 +678,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -723,7 +723,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I5" s="3" t="b">
@@ -768,7 +768,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -813,7 +813,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I7" s="3" t="b">
@@ -858,7 +858,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -903,7 +903,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I9" s="3" t="b">
@@ -948,7 +948,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -993,7 +993,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I11" s="3" t="b">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I13" s="3" t="b">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I15" s="3" t="b">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I16" s="2" t="b">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I17" s="3" t="b">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I18" s="2" t="b">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I19" s="3" t="b">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I20" s="2" t="b">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I21" s="3" t="b">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I22" s="2" t="b">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I23" s="3" t="b">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I24" s="2" t="b">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I25" s="3" t="b">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I26" s="2" t="b">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I27" s="3" t="b">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I28" s="2" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I29" s="3" t="b">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I30" s="2" t="b">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I31" s="3" t="b">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
